--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/97.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/97.xlsx
@@ -426,13 +426,13 @@
         <v>-1.515166414260032</v>
       </c>
       <c r="E2">
-        <v>-9.211339356391822</v>
+        <v>-9.188850954469732</v>
       </c>
       <c r="F2">
-        <v>-4.690982621745898</v>
+        <v>-4.604293144675527</v>
       </c>
       <c r="G2">
-        <v>-7.944767515450742</v>
+        <v>-8.128191601599601</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.452595287502729</v>
       </c>
       <c r="E3">
-        <v>-9.237264870085735</v>
+        <v>-9.721521766569973</v>
       </c>
       <c r="F3">
-        <v>-4.358301989107589</v>
+        <v>-4.719107351805746</v>
       </c>
       <c r="G3">
-        <v>-7.55944980958943</v>
+        <v>-8.006221172296234</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.368605414580176</v>
       </c>
       <c r="E4">
-        <v>-8.885615277968109</v>
+        <v>-10.91914464500851</v>
       </c>
       <c r="F4">
-        <v>-4.097898069098342</v>
+        <v>-4.4659234820793</v>
       </c>
       <c r="G4">
-        <v>-7.669866434960742</v>
+        <v>-8.170341467405603</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.256542523530264</v>
       </c>
       <c r="E5">
-        <v>-10.73407496926304</v>
+        <v>-10.72363230820135</v>
       </c>
       <c r="F5">
-        <v>-3.761073114343826</v>
+        <v>-4.164106162134495</v>
       </c>
       <c r="G5">
-        <v>-7.03080865569645</v>
+        <v>-7.244580512803807</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.103022609366562</v>
       </c>
       <c r="E6">
-        <v>-11.51853346466376</v>
+        <v>-11.43340721026757</v>
       </c>
       <c r="F6">
-        <v>-4.513296157110599</v>
+        <v>-4.408065332463366</v>
       </c>
       <c r="G6">
-        <v>-7.969755513181162</v>
+        <v>-7.733412356587052</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.8991750153657396</v>
       </c>
       <c r="E7">
-        <v>-12.56481021329195</v>
+        <v>-12.54787824897727</v>
       </c>
       <c r="F7">
-        <v>-3.731917066867492</v>
+        <v>-4.059818019591648</v>
       </c>
       <c r="G7">
-        <v>-7.480827663577278</v>
+        <v>-7.627905270250479</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.6435737184744852</v>
       </c>
       <c r="E8">
-        <v>-12.71055914922882</v>
+        <v>-13.78553283764362</v>
       </c>
       <c r="F8">
-        <v>-3.425716026627072</v>
+        <v>-4.230570220698113</v>
       </c>
       <c r="G8">
-        <v>-6.981590775164105</v>
+        <v>-7.269386430529567</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3334206959084658</v>
       </c>
       <c r="E9">
-        <v>-14.12928024261786</v>
+        <v>-14.47329935603256</v>
       </c>
       <c r="F9">
-        <v>-3.723100752599497</v>
+        <v>-4.126523961436884</v>
       </c>
       <c r="G9">
-        <v>-6.702472059657072</v>
+        <v>-7.25833582951948</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.02983062613870668</v>
       </c>
       <c r="E10">
-        <v>-14.99821742063167</v>
+        <v>-14.38681908790808</v>
       </c>
       <c r="F10">
-        <v>-3.90964743497514</v>
+        <v>-3.967476591731976</v>
       </c>
       <c r="G10">
-        <v>-7.057720080385185</v>
+        <v>-7.225763371958591</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.4346620887114452</v>
       </c>
       <c r="E11">
-        <v>-15.27263388854848</v>
+        <v>-15.86306538661656</v>
       </c>
       <c r="F11">
-        <v>-4.171122434036207</v>
+        <v>-3.801806424641686</v>
       </c>
       <c r="G11">
-        <v>-5.683297441573663</v>
+        <v>-6.63566194012904</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.8710621747799068</v>
       </c>
       <c r="E12">
-        <v>-16.03018419139562</v>
+        <v>-16.42643925248881</v>
       </c>
       <c r="F12">
-        <v>-4.068532444669099</v>
+        <v>-3.758860545010949</v>
       </c>
       <c r="G12">
-        <v>-6.716770305841185</v>
+        <v>-6.163243781129503</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.324423884479448</v>
       </c>
       <c r="E13">
-        <v>-16.05574289869492</v>
+        <v>-17.80140170154172</v>
       </c>
       <c r="F13">
-        <v>-3.490664172843567</v>
+        <v>-3.807503935638141</v>
       </c>
       <c r="G13">
-        <v>-5.798487873612603</v>
+        <v>-6.345711119617513</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.773000304072739</v>
       </c>
       <c r="E14">
-        <v>-18.11740314627097</v>
+        <v>-17.90973185675321</v>
       </c>
       <c r="F14">
-        <v>-3.779595409470423</v>
+        <v>-3.703438623926648</v>
       </c>
       <c r="G14">
-        <v>-6.114621798794227</v>
+        <v>-5.5754729733596</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.197057756702618</v>
       </c>
       <c r="E15">
-        <v>-18.98263603254651</v>
+        <v>-18.90581047100638</v>
       </c>
       <c r="F15">
-        <v>-3.059838570321572</v>
+        <v>-3.324589762460711</v>
       </c>
       <c r="G15">
-        <v>-5.353871676051865</v>
+        <v>-4.831603322321982</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.573979826972465</v>
       </c>
       <c r="E16">
-        <v>-19.18960993706708</v>
+        <v>-19.52545968337194</v>
       </c>
       <c r="F16">
-        <v>-3.364604049852941</v>
+        <v>-3.411542660365172</v>
       </c>
       <c r="G16">
-        <v>-4.381038074427173</v>
+        <v>-4.970550229150733</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.880580426468494</v>
       </c>
       <c r="E17">
-        <v>-18.75177895610948</v>
+        <v>-20.37382400396891</v>
       </c>
       <c r="F17">
-        <v>-3.005486899921688</v>
+        <v>-3.253024617430653</v>
       </c>
       <c r="G17">
-        <v>-4.574608982653899</v>
+        <v>-4.454161404298596</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.103169153969465</v>
       </c>
       <c r="E18">
-        <v>-19.91330989670689</v>
+        <v>-20.55963634945164</v>
       </c>
       <c r="F18">
-        <v>-2.887762638105433</v>
+        <v>-2.912721347951782</v>
       </c>
       <c r="G18">
-        <v>-3.509970642679678</v>
+        <v>-4.297572600291068</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.234052073014265</v>
       </c>
       <c r="E19">
-        <v>-21.40287443747192</v>
+        <v>-22.12619400529508</v>
       </c>
       <c r="F19">
-        <v>-2.019703182833387</v>
+        <v>-2.757210278689426</v>
       </c>
       <c r="G19">
-        <v>-3.748171015321319</v>
+        <v>-4.085883076327912</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.271388645354132</v>
       </c>
       <c r="E20">
-        <v>-22.44948176470267</v>
+        <v>-23.4698013003189</v>
       </c>
       <c r="F20">
-        <v>-1.956863231657016</v>
+        <v>-2.136653749495427</v>
       </c>
       <c r="G20">
-        <v>-4.176608576831638</v>
+        <v>-4.147071889530261</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.221406892136724</v>
       </c>
       <c r="E21">
-        <v>-22.96398433908414</v>
+        <v>-22.87645346498988</v>
       </c>
       <c r="F21">
-        <v>-1.62957195734132</v>
+        <v>-1.862184150986644</v>
       </c>
       <c r="G21">
-        <v>-3.496837708525389</v>
+        <v>-4.259974734601565</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.09458595289091</v>
       </c>
       <c r="E22">
-        <v>-23.82602012271026</v>
+        <v>-23.00667426355445</v>
       </c>
       <c r="F22">
-        <v>-1.507835083825905</v>
+        <v>-1.756021413011262</v>
       </c>
       <c r="G22">
-        <v>-3.827312916983135</v>
+        <v>-4.036165303419136</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.907303554086795</v>
       </c>
       <c r="E23">
-        <v>-24.05130717611785</v>
+        <v>-24.26843391936362</v>
       </c>
       <c r="F23">
-        <v>-1.051419555496628</v>
+        <v>-1.46908571345775</v>
       </c>
       <c r="G23">
-        <v>-4.200533889443951</v>
+        <v>-3.830077222508427</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.676674583735155</v>
       </c>
       <c r="E24">
-        <v>-24.60930121486899</v>
+        <v>-25.24531180382426</v>
       </c>
       <c r="F24">
-        <v>-0.7065370710150817</v>
+        <v>-1.296559977741891</v>
       </c>
       <c r="G24">
-        <v>-3.333316622158628</v>
+        <v>-3.758374116673352</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.41524733622132</v>
       </c>
       <c r="E25">
-        <v>-24.44706410507019</v>
+        <v>-25.45836744893714</v>
       </c>
       <c r="F25">
-        <v>-0.7283628953440431</v>
+        <v>-1.393475650399822</v>
       </c>
       <c r="G25">
-        <v>-3.660686538900538</v>
+        <v>-4.169848442840447</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.133950809224733</v>
       </c>
       <c r="E26">
-        <v>-24.46854718576257</v>
+        <v>-25.87715166821848</v>
       </c>
       <c r="F26">
-        <v>-0.6373112355305298</v>
+        <v>-1.184865402250614</v>
       </c>
       <c r="G26">
-        <v>-3.859001458885039</v>
+        <v>-4.4945666126054</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.83947221574724</v>
       </c>
       <c r="E27">
-        <v>-25.64170724761168</v>
+        <v>-25.52617229025399</v>
       </c>
       <c r="F27">
-        <v>-0.3572576123594757</v>
+        <v>-0.7085897654392188</v>
       </c>
       <c r="G27">
-        <v>-2.76801117641822</v>
+        <v>-3.738371800525076</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.53779138494903</v>
       </c>
       <c r="E28">
-        <v>-25.61829503699203</v>
+        <v>-25.59927997463382</v>
       </c>
       <c r="F28">
-        <v>-0.6576774764957585</v>
+        <v>-0.6740004561679227</v>
       </c>
       <c r="G28">
-        <v>-4.115264167988943</v>
+        <v>-4.282738045729594</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.23849792175963</v>
       </c>
       <c r="E29">
-        <v>-24.27347863940817</v>
+        <v>-24.79302140536017</v>
       </c>
       <c r="F29">
-        <v>-0.1065928079049425</v>
+        <v>-0.633389744245677</v>
       </c>
       <c r="G29">
-        <v>-5.234513267178982</v>
+        <v>-4.605827427089227</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.9488347288636766</v>
       </c>
       <c r="E30">
-        <v>-24.89032925483699</v>
+        <v>-25.311866786315</v>
       </c>
       <c r="F30">
-        <v>-0.4521537252893815</v>
+        <v>-0.7642411442940953</v>
       </c>
       <c r="G30">
-        <v>-4.210541668609168</v>
+        <v>-4.924699173431828</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.6766026972255282</v>
       </c>
       <c r="E31">
-        <v>-26.09810044352672</v>
+        <v>-24.7646414587541</v>
       </c>
       <c r="F31">
-        <v>-0.1263162357655988</v>
+        <v>-0.7509665566642332</v>
       </c>
       <c r="G31">
-        <v>-5.768699584850241</v>
+        <v>-4.961254217276459</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.4323000699581332</v>
       </c>
       <c r="E32">
-        <v>-24.59757246718912</v>
+        <v>-24.35706068416774</v>
       </c>
       <c r="F32">
-        <v>-0.8322848994948522</v>
+        <v>-0.6781058450161971</v>
       </c>
       <c r="G32">
-        <v>-3.847672772049653</v>
+        <v>-4.944466440846815</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2227934590528589</v>
       </c>
       <c r="E33">
-        <v>-23.81416004928417</v>
+        <v>-24.33988871073065</v>
       </c>
       <c r="F33">
-        <v>-0.4391392450239985</v>
+        <v>-1.039749515525988</v>
       </c>
       <c r="G33">
-        <v>-5.038919615627761</v>
+        <v>-5.027316153512616</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.0540821813843007</v>
       </c>
       <c r="E34">
-        <v>-22.48066030824548</v>
+        <v>-23.95354647924026</v>
       </c>
       <c r="F34">
-        <v>-0.1330119294824272</v>
+        <v>-0.8698778689686993</v>
       </c>
       <c r="G34">
-        <v>-5.332535210051263</v>
+        <v>-5.445808836222965</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.06760471749962393</v>
       </c>
       <c r="E35">
-        <v>-23.11192052796671</v>
+        <v>-23.98903160156437</v>
       </c>
       <c r="F35">
-        <v>-0.260671629927859</v>
+        <v>-0.8459115432709041</v>
       </c>
       <c r="G35">
-        <v>-4.938368415963478</v>
+        <v>-5.502680698042105</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.1401167550592568</v>
       </c>
       <c r="E36">
-        <v>-22.6544812545559</v>
+        <v>-23.0630265941059</v>
       </c>
       <c r="F36">
-        <v>-0.2693794280660874</v>
+        <v>-0.8993768605497926</v>
       </c>
       <c r="G36">
-        <v>-5.852380244446399</v>
+        <v>-5.923421241173619</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.1632646142432449</v>
       </c>
       <c r="E37">
-        <v>-22.8945311332285</v>
+        <v>-22.14889524549553</v>
       </c>
       <c r="F37">
-        <v>-0.6040224630816289</v>
+        <v>-0.9552560404404389</v>
       </c>
       <c r="G37">
-        <v>-5.423254089463911</v>
+        <v>-5.923609942269358</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1375002183471963</v>
       </c>
       <c r="E38">
-        <v>-22.15727292240972</v>
+        <v>-21.92681435168537</v>
       </c>
       <c r="F38">
-        <v>-0.8095478710228114</v>
+        <v>-0.9266583125935915</v>
       </c>
       <c r="G38">
-        <v>-5.61308408123126</v>
+        <v>-5.824263781181369</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.06539126970391942</v>
       </c>
       <c r="E39">
-        <v>-19.24124812617654</v>
+        <v>-21.79779812720685</v>
       </c>
       <c r="F39">
-        <v>-0.661463943893955</v>
+        <v>-1.083334894791687</v>
       </c>
       <c r="G39">
-        <v>-6.154109985986653</v>
+        <v>-5.061914664943539</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.0484905787826598</v>
       </c>
       <c r="E40">
-        <v>-19.93003355121721</v>
+        <v>-20.71608154099463</v>
       </c>
       <c r="F40">
-        <v>-0.963712843255619</v>
+        <v>-1.111033844006497</v>
       </c>
       <c r="G40">
-        <v>-5.250251600672677</v>
+        <v>-5.379813110897595</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.1989046842730467</v>
       </c>
       <c r="E41">
-        <v>-19.4974510716345</v>
+        <v>-20.39033482020087</v>
       </c>
       <c r="F41">
-        <v>-0.829302776844774</v>
+        <v>-1.26538685563974</v>
       </c>
       <c r="G41">
-        <v>-4.23138155277888</v>
+        <v>-4.598868660365678</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3804147619662368</v>
       </c>
       <c r="E42">
-        <v>-18.69352919494882</v>
+        <v>-19.57045912958617</v>
       </c>
       <c r="F42">
-        <v>-1.604416924420508</v>
+        <v>-1.295129387237256</v>
       </c>
       <c r="G42">
-        <v>-4.883271006553388</v>
+        <v>-5.443895340901267</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5854351318335596</v>
       </c>
       <c r="E43">
-        <v>-18.88450400080029</v>
+        <v>-18.63723573455946</v>
       </c>
       <c r="F43">
-        <v>-1.036805497776439</v>
+        <v>-1.427967212317588</v>
       </c>
       <c r="G43">
-        <v>-5.438376661487301</v>
+        <v>-5.275050897307358</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.8056268179286776</v>
       </c>
       <c r="E44">
-        <v>-18.63989394880197</v>
+        <v>-18.13284071416312</v>
       </c>
       <c r="F44">
-        <v>-1.332396808321803</v>
+        <v>-1.401121481527662</v>
       </c>
       <c r="G44">
-        <v>-5.936411821869719</v>
+        <v>-4.793495632619432</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.033425261465584</v>
       </c>
       <c r="E45">
-        <v>-16.48669512763486</v>
+        <v>-17.42659349334887</v>
       </c>
       <c r="F45">
-        <v>-1.582694646016896</v>
+        <v>-1.536444408816392</v>
       </c>
       <c r="G45">
-        <v>-4.998521028412036</v>
+        <v>-5.097787736407081</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.259698385332032</v>
       </c>
       <c r="E46">
-        <v>-16.58227762851476</v>
+        <v>-16.4465094492908</v>
       </c>
       <c r="F46">
-        <v>-1.350005414203112</v>
+        <v>-1.746262416638881</v>
       </c>
       <c r="G46">
-        <v>-5.215610052149743</v>
+        <v>-5.00794946210788</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.475949295764285</v>
       </c>
       <c r="E47">
-        <v>-15.8609053045149</v>
+        <v>-15.82769800461665</v>
       </c>
       <c r="F47">
-        <v>-1.12252744172034</v>
+        <v>-1.547780616723703</v>
       </c>
       <c r="G47">
-        <v>-4.496900547210586</v>
+        <v>-5.254979059702756</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.676053299809225</v>
       </c>
       <c r="E48">
-        <v>-16.36407763692917</v>
+        <v>-15.15221723621052</v>
       </c>
       <c r="F48">
-        <v>-1.633111571253483</v>
+        <v>-1.726891044924415</v>
       </c>
       <c r="G48">
-        <v>-3.505796044754657</v>
+        <v>-4.488097806621664</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.853355362380851</v>
       </c>
       <c r="E49">
-        <v>-14.0660718024188</v>
+        <v>-15.00332553931232</v>
       </c>
       <c r="F49">
-        <v>-1.50488361076973</v>
+        <v>-1.710695633832282</v>
       </c>
       <c r="G49">
-        <v>-5.343817549249098</v>
+        <v>-4.631305385559457</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.002637673315202</v>
       </c>
       <c r="E50">
-        <v>-13.49408930745797</v>
+        <v>-15.09892615408825</v>
       </c>
       <c r="F50">
-        <v>-1.527865835993</v>
+        <v>-1.909618125205749</v>
       </c>
       <c r="G50">
-        <v>-3.960459748027083</v>
+        <v>-4.527744899999976</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.120432037215074</v>
       </c>
       <c r="E51">
-        <v>-13.92063533118846</v>
+        <v>-14.310613927307</v>
       </c>
       <c r="F51">
-        <v>-1.835959695748817</v>
+        <v>-1.841781461855692</v>
       </c>
       <c r="G51">
-        <v>-4.022075621603999</v>
+        <v>-5.017993657274029</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.202805011200135</v>
       </c>
       <c r="E52">
-        <v>-12.44035416213915</v>
+        <v>-13.64643170155001</v>
       </c>
       <c r="F52">
-        <v>-1.554051357962895</v>
+        <v>-2.215905315656061</v>
       </c>
       <c r="G52">
-        <v>-5.041044985863974</v>
+        <v>-4.936378778094376</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.247177846489029</v>
       </c>
       <c r="E53">
-        <v>-11.98870680698414</v>
+        <v>-13.66488976160527</v>
       </c>
       <c r="F53">
-        <v>-1.778872756184889</v>
+        <v>-1.920629613091163</v>
       </c>
       <c r="G53">
-        <v>-4.824770356328926</v>
+        <v>-5.695056499329154</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.252047842607058</v>
       </c>
       <c r="E54">
-        <v>-11.95136501031689</v>
+        <v>-12.44741405311711</v>
       </c>
       <c r="F54">
-        <v>-2.235583183309563</v>
+        <v>-2.296590785790941</v>
       </c>
       <c r="G54">
-        <v>-4.892004225685985</v>
+        <v>-5.89593709210659</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.21647083053527</v>
       </c>
       <c r="E55">
-        <v>-9.678691459405426</v>
+        <v>-11.93734938326316</v>
       </c>
       <c r="F55">
-        <v>-1.85143608393532</v>
+        <v>-1.938071717124509</v>
       </c>
       <c r="G55">
-        <v>-4.322107053282607</v>
+        <v>-5.266943371281682</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.141371727047407</v>
       </c>
       <c r="E56">
-        <v>-12.39907712155923</v>
+        <v>-11.83799919200887</v>
       </c>
       <c r="F56">
-        <v>-1.923387248175083</v>
+        <v>-1.820975357799577</v>
       </c>
       <c r="G56">
-        <v>-4.925579778545274</v>
+        <v>-5.517260340597056</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.02825437845226</v>
       </c>
       <c r="E57">
-        <v>-11.18381583686081</v>
+        <v>-10.91763666316396</v>
       </c>
       <c r="F57">
-        <v>-2.067422943806458</v>
+        <v>-1.802906179642311</v>
       </c>
       <c r="G57">
-        <v>-5.223694404356643</v>
+        <v>-6.305583997136007</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.880537710407671</v>
       </c>
       <c r="E58">
-        <v>-10.11661753831719</v>
+        <v>-10.37021208274673</v>
       </c>
       <c r="F58">
-        <v>-1.938286264281835</v>
+        <v>-2.05240961299812</v>
       </c>
       <c r="G58">
-        <v>-5.461795460632106</v>
+        <v>-5.835814274567886</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.703233614078133</v>
       </c>
       <c r="E59">
-        <v>-9.903281127815838</v>
+        <v>-10.27909012876439</v>
       </c>
       <c r="F59">
-        <v>-2.021696234804522</v>
+        <v>-2.109919848304878</v>
       </c>
       <c r="G59">
-        <v>-5.325132830225452</v>
+        <v>-5.892096859281035</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.501127274147011</v>
       </c>
       <c r="E60">
-        <v>-8.639325162112941</v>
+        <v>-9.603496148508061</v>
       </c>
       <c r="F60">
-        <v>-2.353379513089861</v>
+        <v>-2.364229469331729</v>
       </c>
       <c r="G60">
-        <v>-5.784183006337413</v>
+        <v>-5.851559229152659</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.281419258566346</v>
       </c>
       <c r="E61">
-        <v>-9.512048144397165</v>
+        <v>-10.44059362577394</v>
       </c>
       <c r="F61">
-        <v>-2.069966860100455</v>
+        <v>-2.075781999268107</v>
       </c>
       <c r="G61">
-        <v>-6.138871544869389</v>
+        <v>-6.218195526535865</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.051847526092585</v>
       </c>
       <c r="E62">
-        <v>-9.276830147490751</v>
+        <v>-9.685787578175447</v>
       </c>
       <c r="F62">
-        <v>-2.341924020276547</v>
+        <v>-2.084012657782324</v>
       </c>
       <c r="G62">
-        <v>-5.734130868329172</v>
+        <v>-6.173331013387662</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.8182619423298169</v>
       </c>
       <c r="E63">
-        <v>-8.048929891836925</v>
+        <v>-8.799003684097405</v>
       </c>
       <c r="F63">
-        <v>-2.252828964268446</v>
+        <v>-2.154978893180157</v>
       </c>
       <c r="G63">
-        <v>-6.564048219023526</v>
+        <v>-6.406558946629318</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.5883664366015527</v>
       </c>
       <c r="E64">
-        <v>-8.623516259352163</v>
+        <v>-8.869539195240879</v>
       </c>
       <c r="F64">
-        <v>-1.936949279293716</v>
+        <v>-2.130506434999251</v>
       </c>
       <c r="G64">
-        <v>-6.210054895054798</v>
+        <v>-6.872332840731538</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.3689515151460271</v>
       </c>
       <c r="E65">
-        <v>-8.357749176790007</v>
+        <v>-8.652032060178465</v>
       </c>
       <c r="F65">
-        <v>-2.461382883434263</v>
+        <v>-2.500799089561673</v>
       </c>
       <c r="G65">
-        <v>-6.677878016845827</v>
+        <v>-6.882936518093823</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.1642852495632171</v>
       </c>
       <c r="E66">
-        <v>-7.837504497366813</v>
+        <v>-8.595014043947886</v>
       </c>
       <c r="F66">
-        <v>-2.357393781523828</v>
+        <v>-2.453752791287077</v>
       </c>
       <c r="G66">
-        <v>-6.089991339982049</v>
+        <v>-6.199444596601433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.01984783824919699</v>
       </c>
       <c r="E67">
-        <v>-6.906495526129864</v>
+        <v>-8.60898438626155</v>
       </c>
       <c r="F67">
-        <v>-2.12009634184827</v>
+        <v>-2.496915703177348</v>
       </c>
       <c r="G67">
-        <v>-6.370702427893471</v>
+        <v>-6.746856543702081</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.17890883164198</v>
       </c>
       <c r="E68">
-        <v>-7.852824324934761</v>
+        <v>-8.636780159720631</v>
       </c>
       <c r="F68">
-        <v>-2.798372683301936</v>
+        <v>-2.244372989820669</v>
       </c>
       <c r="G68">
-        <v>-6.567021088917792</v>
+        <v>-6.078262077136412</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.3107335886274813</v>
       </c>
       <c r="E69">
-        <v>-8.024290464761192</v>
+        <v>-8.126561521750419</v>
       </c>
       <c r="F69">
-        <v>-2.41377495206057</v>
+        <v>-2.33697452504482</v>
       </c>
       <c r="G69">
-        <v>-6.767153498403353</v>
+        <v>-6.442852457376348</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.4127803064754716</v>
       </c>
       <c r="E70">
-        <v>-8.632079603700669</v>
+        <v>-8.512813183760654</v>
       </c>
       <c r="F70">
-        <v>-2.738618400700993</v>
+        <v>-2.68956331147461</v>
       </c>
       <c r="G70">
-        <v>-6.911953449745535</v>
+        <v>-6.680367547091358</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.4840776964087009</v>
       </c>
       <c r="E71">
-        <v>-7.609944150007369</v>
+        <v>-7.672989565142156</v>
       </c>
       <c r="F71">
-        <v>-2.927887098362236</v>
+        <v>-2.731176347954243</v>
       </c>
       <c r="G71">
-        <v>-6.387374335229241</v>
+        <v>-6.453346886735837</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5252205477311477</v>
       </c>
       <c r="E72">
-        <v>-8.196838909875455</v>
+        <v>-9.123514131487063</v>
       </c>
       <c r="F72">
-        <v>-3.337167693104818</v>
+        <v>-2.886831553144687</v>
       </c>
       <c r="G72">
-        <v>-5.31528726779166</v>
+        <v>-6.440985309692199</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.5365750192862802</v>
       </c>
       <c r="E73">
-        <v>-8.365130589422508</v>
+        <v>-8.645420488127266</v>
       </c>
       <c r="F73">
-        <v>-3.024051441785828</v>
+        <v>-3.064737535141728</v>
       </c>
       <c r="G73">
-        <v>-6.663477143749997</v>
+        <v>-6.559026121440452</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5184753269915542</v>
       </c>
       <c r="E74">
-        <v>-7.178163210324016</v>
+        <v>-9.298652863733714</v>
       </c>
       <c r="F74">
-        <v>-3.283845683386614</v>
+        <v>-2.742150559306531</v>
       </c>
       <c r="G74">
-        <v>-6.002043387185771</v>
+        <v>-6.459292626524368</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.4712995163723691</v>
       </c>
       <c r="E75">
-        <v>-8.490496863850854</v>
+        <v>-9.705894002769503</v>
       </c>
       <c r="F75">
-        <v>-3.110040948400833</v>
+        <v>-2.913664858423571</v>
       </c>
       <c r="G75">
-        <v>-5.316383058365158</v>
+        <v>-5.553226107335697</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3958788421719015</v>
       </c>
       <c r="E76">
-        <v>-9.421261297491389</v>
+        <v>-9.471880579949129</v>
       </c>
       <c r="F76">
-        <v>-3.084662256281265</v>
+        <v>-2.866004739903502</v>
       </c>
       <c r="G76">
-        <v>-5.003470293993246</v>
+        <v>-5.723133236047713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.2920313501071407</v>
       </c>
       <c r="E77">
-        <v>-8.780020321057252</v>
+        <v>-9.82029231315127</v>
       </c>
       <c r="F77">
-        <v>-2.771290867802212</v>
+        <v>-3.269100743616783</v>
       </c>
       <c r="G77">
-        <v>-5.576757465028837</v>
+        <v>-5.455498803016412</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.1594167612932092</v>
       </c>
       <c r="E78">
-        <v>-10.03322568946594</v>
+        <v>-10.74699470560692</v>
       </c>
       <c r="F78">
-        <v>-3.299122435029043</v>
+        <v>-3.238426298691117</v>
       </c>
       <c r="G78">
-        <v>-4.930505870307709</v>
+        <v>-5.565286424735262</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.0001254647840152023</v>
       </c>
       <c r="E79">
-        <v>-9.594819592309364</v>
+        <v>-11.66394276505006</v>
       </c>
       <c r="F79">
-        <v>-2.916386045341767</v>
+        <v>-3.363885855314714</v>
       </c>
       <c r="G79">
-        <v>-5.060239528900668</v>
+        <v>-5.243080959034615</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.1852643279148564</v>
       </c>
       <c r="E80">
-        <v>-9.478505737422351</v>
+        <v>-10.99834765540267</v>
       </c>
       <c r="F80">
-        <v>-3.203221512439541</v>
+        <v>-3.191876192490799</v>
       </c>
       <c r="G80">
-        <v>-5.310672367309915</v>
+        <v>-4.824939194151429</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3958718516782158</v>
       </c>
       <c r="E81">
-        <v>-12.01039819748089</v>
+        <v>-12.11554936393899</v>
       </c>
       <c r="F81">
-        <v>-3.162214840898757</v>
+        <v>-3.51694661379959</v>
       </c>
       <c r="G81">
-        <v>-3.972930573073518</v>
+        <v>-5.046686155462892</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6272966702415941</v>
       </c>
       <c r="E82">
-        <v>-14.07008403038959</v>
+        <v>-12.91381970506311</v>
       </c>
       <c r="F82">
-        <v>-3.658947010722287</v>
+        <v>-3.573018803295088</v>
       </c>
       <c r="G82">
-        <v>-3.222297477499169</v>
+        <v>-4.326311446117481</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8772063863724748</v>
       </c>
       <c r="E83">
-        <v>-13.90827712562153</v>
+        <v>-13.93345544110417</v>
       </c>
       <c r="F83">
-        <v>-3.664585707633143</v>
+        <v>-3.489338784999088</v>
       </c>
       <c r="G83">
-        <v>-3.225644439039372</v>
+        <v>-4.227945206509117</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.141653337491473</v>
       </c>
       <c r="E84">
-        <v>-13.71053677960259</v>
+        <v>-14.99228059120762</v>
       </c>
       <c r="F84">
-        <v>-3.52968524771984</v>
+        <v>-3.45078987954241</v>
       </c>
       <c r="G84">
-        <v>-3.451562687730316</v>
+        <v>-4.128857267973191</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.411377903021634</v>
       </c>
       <c r="E85">
-        <v>-16.35268852479988</v>
+        <v>-15.25094702652575</v>
       </c>
       <c r="F85">
-        <v>-3.959724729576579</v>
+        <v>-3.782318253123425</v>
       </c>
       <c r="G85">
-        <v>-3.697082676559285</v>
+        <v>-3.796458632557128</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.67830947400308</v>
       </c>
       <c r="E86">
-        <v>-17.47818186924425</v>
+        <v>-16.34414782282142</v>
       </c>
       <c r="F86">
-        <v>-3.267650272294481</v>
+        <v>-3.529876600589887</v>
       </c>
       <c r="G86">
-        <v>-3.68797867632629</v>
+        <v>-3.740195911117214</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.93246257456955</v>
       </c>
       <c r="E87">
-        <v>-17.5154059255873</v>
+        <v>-17.74481389034187</v>
       </c>
       <c r="F87">
-        <v>-4.034177563372795</v>
+        <v>-3.687900936552337</v>
       </c>
       <c r="G87">
-        <v>-3.440588229267632</v>
+        <v>-3.815769044687697</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.160607056703919</v>
       </c>
       <c r="E88">
-        <v>-19.08861590974801</v>
+        <v>-19.95000412159104</v>
       </c>
       <c r="F88">
-        <v>-4.049002026413295</v>
+        <v>-3.799259194878078</v>
       </c>
       <c r="G88">
-        <v>-4.048573228100325</v>
+        <v>-3.765766564862545</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.352009321336846</v>
       </c>
       <c r="E89">
-        <v>-20.84003946000659</v>
+        <v>-21.93604338171301</v>
       </c>
       <c r="F89">
-        <v>-3.855112695379237</v>
+        <v>-3.934842229531287</v>
       </c>
       <c r="G89">
-        <v>-2.872306603087419</v>
+        <v>-3.387602947911597</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.496168057359662</v>
       </c>
       <c r="E90">
-        <v>-22.12162930349535</v>
+        <v>-21.99003184883245</v>
       </c>
       <c r="F90">
-        <v>-3.739194274501086</v>
+        <v>-3.609385789012792</v>
       </c>
       <c r="G90">
-        <v>-3.24845740835049</v>
+        <v>-4.157443828704798</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.583075815195912</v>
       </c>
       <c r="E91">
-        <v>-24.58590711814536</v>
+        <v>-24.43349679694321</v>
       </c>
       <c r="F91">
-        <v>-4.255916606488973</v>
+        <v>-4.002471801030644</v>
       </c>
       <c r="G91">
-        <v>-3.141109658694083</v>
+        <v>-3.505597412022301</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.606624108241486</v>
       </c>
       <c r="E92">
-        <v>-26.43806204423055</v>
+        <v>-25.67943849304359</v>
       </c>
       <c r="F92">
-        <v>-4.062793515302504</v>
+        <v>-4.11177819329965</v>
       </c>
       <c r="G92">
-        <v>-3.727443689699942</v>
+        <v>-4.334250134320654</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.563442583654266</v>
       </c>
       <c r="E93">
-        <v>-27.16018609491569</v>
+        <v>-27.22665956487428</v>
       </c>
       <c r="F93">
-        <v>-3.967100512931105</v>
+        <v>-4.000665960092541</v>
       </c>
       <c r="G93">
-        <v>-4.46899264831453</v>
+        <v>-3.980501790721831</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.45481777218298</v>
       </c>
       <c r="E94">
-        <v>-29.91173218671628</v>
+        <v>-29.18883829544983</v>
       </c>
       <c r="F94">
-        <v>-3.501064325585715</v>
+        <v>-3.923584716527242</v>
       </c>
       <c r="G94">
-        <v>-3.77314577086958</v>
+        <v>-4.789748095068976</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.287850993469131</v>
       </c>
       <c r="E95">
-        <v>-31.53223302493909</v>
+        <v>-30.87727530073572</v>
       </c>
       <c r="F95">
-        <v>-3.336268086105378</v>
+        <v>-4.008428591024176</v>
       </c>
       <c r="G95">
-        <v>-4.757125979324998</v>
+        <v>-4.921295932617456</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.071076779932667</v>
       </c>
       <c r="E96">
-        <v>-33.93535379811551</v>
+        <v>-33.89151364124726</v>
       </c>
       <c r="F96">
-        <v>-4.220112910605172</v>
+        <v>-3.992778245683084</v>
       </c>
       <c r="G96">
-        <v>-4.154242531168323</v>
+        <v>-4.69493407082425</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.820680545547147</v>
       </c>
       <c r="E97">
-        <v>-36.155497050538</v>
+        <v>-36.2674296068226</v>
       </c>
       <c r="F97">
-        <v>-4.091055754351218</v>
+        <v>-4.142571094763916</v>
       </c>
       <c r="G97">
-        <v>-5.021251234084671</v>
+        <v>-5.639694246275922</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.549127187051794</v>
       </c>
       <c r="E98">
-        <v>-37.76286304990157</v>
+        <v>-37.51122027776934</v>
       </c>
       <c r="F98">
-        <v>-3.541434810961149</v>
+        <v>-3.864626495000389</v>
       </c>
       <c r="G98">
-        <v>-5.584861680508973</v>
+        <v>-5.989678499596593</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.277037668627939</v>
       </c>
       <c r="E99">
-        <v>-40.89494360527771</v>
+        <v>-40.42249244053147</v>
       </c>
       <c r="F99">
-        <v>-4.289136624443441</v>
+        <v>-3.84722498096978</v>
       </c>
       <c r="G99">
-        <v>-6.032841392337611</v>
+        <v>-5.608340069473484</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.012272849365034</v>
       </c>
       <c r="E100">
-        <v>-43.39101583593557</v>
+        <v>-43.49234723456821</v>
       </c>
       <c r="F100">
-        <v>-3.671995454051184</v>
+        <v>-4.176433925822957</v>
       </c>
       <c r="G100">
-        <v>-6.164965264809924</v>
+        <v>-6.778856276884676</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.7829192606773635</v>
       </c>
       <c r="E101">
-        <v>-45.95867418370668</v>
+        <v>-45.32777624190607</v>
       </c>
       <c r="F101">
-        <v>-4.092990820604157</v>
+        <v>-4.387224436976333</v>
       </c>
       <c r="G101">
-        <v>-6.672663907621475</v>
+        <v>-6.694622756183461</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.5750655898582083</v>
       </c>
       <c r="E102">
-        <v>-47.21215805326685</v>
+        <v>-47.59866330982151</v>
       </c>
       <c r="F102">
-        <v>-3.713862799323477</v>
+        <v>-4.210867502022527</v>
       </c>
       <c r="G102">
-        <v>-6.403066321085386</v>
+        <v>-7.524169325777416</v>
       </c>
     </row>
   </sheetData>
